--- a/exports/OFSS_full_report.xlsx
+++ b/exports/OFSS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>6.15</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.38541666666</v>
+        <v>44579.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>3586</v>
+        <v>3529.5</v>
       </c>
       <c r="I2" t="n">
         <v>3552.6783868</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.24</v>
+        <v>-2.8</v>
       </c>
       <c r="L2" t="n">
-        <v>3.17</v>
+        <v>3.36</v>
       </c>
       <c r="M2" t="n">
         <v>-0</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.27</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>3128</v>
+        <v>3312.5</v>
       </c>
       <c r="I3" t="n">
         <v>3219.351098981542</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>11.38</v>
+        <v>6.15</v>
       </c>
       <c r="L3" t="n">
         <v>1.76</v>
@@ -612,7 +647,7 @@
         <v>1.69</v>
       </c>
       <c r="N3" t="n">
-        <v>3.15</v>
+        <v>5.45</v>
       </c>
       <c r="O3" t="n">
         <v>-2.14</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>10.66</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44613.55208333334</v>
+        <v>44614.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>3093</v>
+        <v>2982</v>
       </c>
       <c r="I4" t="n">
         <v>3055.44841160615</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.63</v>
+        <v>-9.98</v>
       </c>
       <c r="L4" t="n">
-        <v>7.15</v>
+        <v>10.4</v>
       </c>
       <c r="M4" t="n">
         <v>1.95</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.27</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44637.38541666666</v>
+        <v>44637.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>3093</v>
+        <v>3139</v>
       </c>
       <c r="I5" t="n">
         <v>3113.40391401435</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.72</v>
+        <v>-5.26</v>
       </c>
       <c r="L5" t="n">
-        <v>5.18</v>
+        <v>5.26</v>
       </c>
       <c r="M5" t="n">
         <v>1.46</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>6.2</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>3136</v>
+        <v>3113</v>
       </c>
       <c r="I6" t="n">
         <v>3132.906199880034</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>27</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1</v>
+        <v>-0.83</v>
       </c>
       <c r="L6" t="n">
         <v>2.93</v>
       </c>
       <c r="M6" t="n">
-        <v>0.45</v>
+        <v>2.07</v>
       </c>
       <c r="N6" t="n">
         <v>2.53</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>4.6</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44711.38541666666</v>
+        <v>44711.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>2872.5</v>
+        <v>2880.5</v>
       </c>
       <c r="I7" t="n">
         <v>2873.437822517189</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>7.73</v>
+        <v>7.47</v>
       </c>
       <c r="L7" t="n">
         <v>3.18</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>7.13</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>2765</v>
+        <v>2713.5</v>
       </c>
       <c r="I8" t="n">
         <v>2763.37833064674</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.01</v>
+        <v>-5.8</v>
       </c>
       <c r="L8" t="n">
-        <v>5.47</v>
+        <v>6.47</v>
       </c>
       <c r="M8" t="n">
-        <v>0.66</v>
+        <v>2.22</v>
       </c>
       <c r="N8" t="n">
-        <v>1.54</v>
+        <v>3.06</v>
       </c>
       <c r="O8" t="n">
         <v>3.91</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>5.74</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>2714</v>
+        <v>2759.5</v>
       </c>
       <c r="I9" t="n">
         <v>2746.838680794876</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.02</v>
+        <v>-1.7</v>
       </c>
       <c r="L9" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="M9" t="n">
         <v>1.59</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.46</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44768.38541666666</v>
+        <v>44768.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>2727</v>
+        <v>2688.5</v>
       </c>
       <c r="I10" t="n">
         <v>2709.047012338809</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.18</v>
+        <v>-2.57</v>
       </c>
       <c r="L10" t="n">
         <v>5.06</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>5.86</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44774.55208333334</v>
+        <v>44775.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>2756</v>
+        <v>2836</v>
       </c>
       <c r="I11" t="n">
         <v>2782.639066044087</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.51</v>
+        <v>-5.49</v>
       </c>
       <c r="L11" t="n">
-        <v>3.48</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M11" t="n">
         <v>0.98</v>
       </c>
       <c r="N11" t="n">
-        <v>1.96</v>
+        <v>3.97</v>
       </c>
       <c r="O11" t="n">
         <v>-4.54</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.37</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44796.55208333334</v>
+        <v>44797.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>2835.5</v>
+        <v>2802</v>
       </c>
       <c r="I12" t="n">
         <v>2821.813082071286</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.02</v>
+        <v>-1.2</v>
       </c>
       <c r="L12" t="n">
         <v>3.31</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>5.18</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44813.55208333334</v>
+        <v>44816.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>2754.5</v>
+        <v>2793</v>
       </c>
       <c r="I13" t="n">
         <v>2775.940650316418</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7</v>
+        <v>0.32</v>
       </c>
       <c r="L13" t="n">
         <v>1.75</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>4.69</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>2708</v>
+        <v>2642</v>
       </c>
       <c r="I14" t="n">
         <v>2683.850982719673</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.04</v>
+        <v>-5.41</v>
       </c>
       <c r="L14" t="n">
-        <v>3.62</v>
+        <v>5.8</v>
       </c>
       <c r="M14" t="n">
         <v>1.72</v>
       </c>
       <c r="N14" t="n">
-        <v>2.41</v>
+        <v>2.51</v>
       </c>
       <c r="O14" t="n">
         <v>1.63</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.85</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44867.38541666666</v>
+        <v>44867.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>2569</v>
+        <v>2584.5</v>
       </c>
       <c r="I15" t="n">
         <v>2578.208120876639</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>47</v>
+        <v>47.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>2.76</v>
+        <v>2.18</v>
       </c>
       <c r="L15" t="n">
         <v>2.5</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>3.35</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>2687.5</v>
+        <v>2660</v>
       </c>
       <c r="I16" t="n">
         <v>2674.15573295064</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K16" t="n">
-        <v>3.99</v>
+        <v>2.92</v>
       </c>
       <c r="L16" t="n">
         <v>0.85</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.26</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44938.55208333334</v>
+        <v>44939.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>2651.5</v>
+        <v>2686.5</v>
       </c>
       <c r="I17" t="n">
         <v>2667.287413779081</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K17" t="n">
-        <v>0.32</v>
+        <v>-1</v>
       </c>
       <c r="L17" t="n">
         <v>1.94</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>3.76</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44958.38541666666</v>
+        <v>44958.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>2669</v>
+        <v>2619</v>
       </c>
       <c r="I18" t="n">
         <v>2623.854263574592</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.65</v>
+        <v>-2.51</v>
       </c>
       <c r="L18" t="n">
-        <v>2.46</v>
+        <v>2.77</v>
       </c>
       <c r="M18" t="n">
         <v>0.7</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>5.55</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44965.55208333334</v>
+        <v>44966.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>2757</v>
+        <v>2771</v>
       </c>
       <c r="I19" t="n">
         <v>2764.460751947313</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.27</v>
+        <v>-5.8</v>
       </c>
       <c r="L19" t="n">
-        <v>6.22</v>
+        <v>6.68</v>
       </c>
       <c r="M19" t="n">
         <v>0.61</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>3.86</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45054.55208333334</v>
+        <v>45055.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>3265</v>
+        <v>3026.5</v>
       </c>
       <c r="I20" t="n">
         <v>3149.001971337114</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>88.16666666666667</v>
+        <v>89</v>
       </c>
       <c r="K20" t="n">
-        <v>17.83</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="L20" t="n">
         <v>2.69</v>
       </c>
       <c r="M20" t="n">
-        <v>1.17</v>
+        <v>7.9</v>
       </c>
       <c r="N20" t="n">
-        <v>2.01</v>
+        <v>7.78</v>
       </c>
       <c r="O20" t="n">
         <v>0.76</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>6.55</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45077.55208333334</v>
+        <v>45078.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>3179</v>
+        <v>3199.5</v>
       </c>
       <c r="I21" t="n">
         <v>3194.008403216937</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.04</v>
+        <v>-5.72</v>
       </c>
       <c r="L21" t="n">
-        <v>5.88</v>
+        <v>6.33</v>
       </c>
       <c r="M21" t="n">
-        <v>0.65</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
         <v>1.83</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>3.33</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45085.55208333334</v>
+        <v>45086.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>3107</v>
+        <v>3092</v>
       </c>
       <c r="I22" t="n">
         <v>3092.924455872521</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.89</v>
+        <v>-3.36</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
         <v>0.59</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>4.64</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45089.55208333334</v>
+        <v>45090.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>3157.5</v>
+        <v>3369.5</v>
       </c>
       <c r="I23" t="n">
         <v>3225.271257771956</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.12</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>2.47</v>
+        <v>9.67</v>
       </c>
       <c r="M23" t="n">
-        <v>0.08</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.61</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
         <v>0.02</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>7.87</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45133.38541666666</v>
+        <v>45133.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>3381.5</v>
+        <v>3336</v>
       </c>
       <c r="I24" t="n">
         <v>3351.200904180602</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K24" t="n">
-        <v>0.36</v>
+        <v>-0.99</v>
       </c>
       <c r="L24" t="n">
         <v>5.64</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.67</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45147.38541666666</v>
+        <v>45147.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>3512.5</v>
+        <v>3527.5</v>
       </c>
       <c r="I25" t="n">
         <v>3517.624001722231</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.29</v>
+        <v>-5.74</v>
       </c>
       <c r="L25" t="n">
         <v>5.83</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>4.67</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>3806.5</v>
+        <v>3743.5</v>
       </c>
       <c r="I26" t="n">
         <v>3752.524355596255</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K26" t="n">
-        <v>7.91</v>
+        <v>6.12</v>
       </c>
       <c r="L26" t="n">
         <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="N26" t="n">
         <v>2.67</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>5.45</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>3702</v>
+        <v>3735</v>
       </c>
       <c r="I27" t="n">
         <v>3732.982547939476</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K27" t="n">
-        <v>1.11</v>
+        <v>0.23</v>
       </c>
       <c r="L27" t="n">
         <v>4.63</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.72</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45218.38541666666</v>
+        <v>45218.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>3588.5</v>
+        <v>3554</v>
       </c>
       <c r="I28" t="n">
         <v>3558.680741816447</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.92</v>
+        <v>-4.85</v>
       </c>
       <c r="L28" t="n">
         <v>5.94</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>5.63</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45237.55208333334</v>
+        <v>45238.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>3524.5</v>
+        <v>3604</v>
       </c>
       <c r="I29" t="n">
         <v>3592.61182472465</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>0.83</v>
+        <v>-1.41</v>
       </c>
       <c r="L29" t="n">
-        <v>1.07</v>
+        <v>1.98</v>
       </c>
       <c r="M29" t="n">
         <v>0.95</v>
       </c>
       <c r="N29" t="n">
-        <v>1.77</v>
+        <v>2.27</v>
       </c>
       <c r="O29" t="n">
         <v>-2.4</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.2</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45254.38541666666</v>
+        <v>45254.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>3585</v>
+        <v>3568.5</v>
       </c>
       <c r="I30" t="n">
         <v>3575.829277548421</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.53</v>
+        <v>-0.99</v>
       </c>
       <c r="L30" t="n">
         <v>3.55</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>4.81</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45268.55208333334</v>
+        <v>45271.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>3667</v>
+        <v>3742.5</v>
       </c>
       <c r="I31" t="n">
         <v>3716.361064690665</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.76</v>
+        <v>-4.88</v>
       </c>
       <c r="L31" t="n">
-        <v>3.99</v>
+        <v>5.03</v>
       </c>
       <c r="M31" t="n">
         <v>0.95</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.87</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45281.55208333334</v>
+        <v>45282.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>3730</v>
+        <v>3690</v>
       </c>
       <c r="I32" t="n">
         <v>3708.924065577453</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.33</v>
+        <v>-1.4</v>
       </c>
       <c r="L32" t="n">
         <v>4.25</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>6.81</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45292.55208333334</v>
+        <v>45293.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>3839.5</v>
+        <v>3959.5</v>
       </c>
       <c r="I33" t="n">
         <v>3892.887188348699</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.05</v>
+        <v>-7.3</v>
       </c>
       <c r="L33" t="n">
-        <v>5.12</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M33" t="n">
         <v>1.76</v>
       </c>
       <c r="N33" t="n">
-        <v>2.16</v>
+        <v>3.83</v>
       </c>
       <c r="O33" t="n">
         <v>0.36</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>5.9</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45391.38541666666</v>
+        <v>45391.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>7756.5</v>
+        <v>7681.5</v>
       </c>
       <c r="I34" t="n">
         <v>7695.774042342433</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>98</v>
+        <v>98.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>95.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="L34" t="n">
         <v>3.64</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.34</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45412.55208333334</v>
+        <v>45414.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>6908</v>
+        <v>7066</v>
       </c>
       <c r="I35" t="n">
         <v>7044.86239170757</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>21</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>10.07</v>
+        <v>8.01</v>
       </c>
       <c r="L35" t="n">
         <v>0.98</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>7116.5</v>
+        <v>7053</v>
       </c>
       <c r="I36" t="n">
         <v>7059.219800711043</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K36" t="n">
-        <v>0.71</v>
+        <v>-0.18</v>
       </c>
       <c r="L36" t="n">
         <v>1.95</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>4.25</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45447.55208333334</v>
+        <v>45448.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>6876.5</v>
+        <v>7289.5</v>
       </c>
       <c r="I37" t="n">
         <v>7253.55722401</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K37" t="n">
-        <v>2.5</v>
+        <v>-3.35</v>
       </c>
       <c r="L37" t="n">
-        <v>1.79</v>
+        <v>4.1</v>
       </c>
       <c r="M37" t="n">
         <v>0.82</v>
       </c>
       <c r="N37" t="n">
-        <v>1.34</v>
+        <v>5.54</v>
       </c>
       <c r="O37" t="n">
         <v>-1.46</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.9</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45506.38541666666</v>
+        <v>45506.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>9911</v>
+        <v>9787</v>
       </c>
       <c r="I38" t="n">
         <v>9871.185964953644</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>58</v>
+        <v>58.16666666666666</v>
       </c>
       <c r="K38" t="n">
-        <v>35.96</v>
+        <v>34.26</v>
       </c>
       <c r="L38" t="n">
         <v>5.79</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>7.87</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45516.38541666666</v>
+        <v>45516.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>9985</v>
+        <v>10124</v>
       </c>
       <c r="I39" t="n">
         <v>10117.84939233058</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.02</v>
+        <v>-3.44</v>
       </c>
       <c r="L39" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="M39" t="n">
         <v>2.58</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45552.55208333334</v>
+        <v>45553.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>11553</v>
+        <v>10703.5</v>
       </c>
       <c r="I40" t="n">
         <v>10931.06552409749</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K40" t="n">
-        <v>14.11</v>
+        <v>5.72</v>
       </c>
       <c r="L40" t="n">
         <v>1.37</v>
@@ -2721,7 +3200,7 @@
         <v>1.06</v>
       </c>
       <c r="N40" t="n">
-        <v>3.61</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="O40" t="n">
         <v>1.68</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>12.84</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45573.55208333334</v>
+        <v>45574.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>10596</v>
+        <v>10993</v>
       </c>
       <c r="I41" t="n">
         <v>10979.57081825836</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>-2.7</v>
       </c>
       <c r="L41" t="n">
         <v>8.24</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>10526.5</v>
+        <v>10478</v>
       </c>
       <c r="I42" t="n">
         <v>10522.63701103461</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.24</v>
+        <v>-4.68</v>
       </c>
       <c r="L42" t="n">
-        <v>4.44</v>
+        <v>4.99</v>
       </c>
       <c r="M42" t="n">
         <v>0.63</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>7.24</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>10842</v>
+        <v>11205.5</v>
       </c>
       <c r="I43" t="n">
         <v>11009.3604284618</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.47</v>
+        <v>-6.94</v>
       </c>
       <c r="L43" t="n">
-        <v>5.63</v>
+        <v>7.37</v>
       </c>
       <c r="M43" t="n">
         <v>1.53</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.56</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45663.38541666666</v>
+        <v>45663.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>11391.5</v>
+        <v>11319</v>
       </c>
       <c r="I44" t="n">
         <v>11320.79964238597</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="L44" t="n">
         <v>7.45</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.09</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45737.55208333334</v>
+        <v>45740.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>7201</v>
+        <v>7537.5</v>
       </c>
       <c r="I45" t="n">
         <v>7423.739010132691</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>74</v>
+        <v>76.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>36.38</v>
+        <v>33.41</v>
       </c>
       <c r="L45" t="n">
         <v>1.69</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>9.85</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>7112</v>
+        <v>6735</v>
       </c>
       <c r="I46" t="n">
         <v>6997.198944082729</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.65</v>
+        <v>-10.65</v>
       </c>
       <c r="L46" t="n">
-        <v>6.89</v>
+        <v>12.05</v>
       </c>
       <c r="M46" t="n">
-        <v>1.42</v>
+        <v>4.18</v>
       </c>
       <c r="N46" t="n">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="O46" t="n">
         <v>4.06</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>8.81</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>7318</v>
+        <v>7354</v>
       </c>
       <c r="I47" t="n">
         <v>7328.500776305656</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.66</v>
+        <v>-9.19</v>
       </c>
       <c r="L47" t="n">
-        <v>9</v>
+        <v>9.35</v>
       </c>
       <c r="M47" t="n">
         <v>2.72</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>7.17</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45785.55208333334</v>
+        <v>45786.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>7885</v>
+        <v>7767</v>
       </c>
       <c r="I48" t="n">
         <v>7809.811842836616</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>7.22</v>
+        <v>5.62</v>
       </c>
       <c r="L48" t="n">
         <v>0.7</v>
       </c>
       <c r="M48" t="n">
-        <v>1.37</v>
+        <v>1.98</v>
       </c>
       <c r="N48" t="n">
         <v>3.29</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>6.87</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>7792</v>
+        <v>8392.5</v>
       </c>
       <c r="I49" t="n">
         <v>8227.105301597234</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.32</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>1.57</v>
+        <v>8.27</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O49" t="n">
         <v>-1.18</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45831.38541666666</v>
+        <v>45831.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>8987.5</v>
+        <v>8890</v>
       </c>
       <c r="I50" t="n">
         <v>8964.113222887087</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K50" t="n">
-        <v>7.09</v>
+        <v>5.93</v>
       </c>
       <c r="L50" t="n">
         <v>5.26</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.98</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>8373</v>
+        <v>8552</v>
       </c>
       <c r="I51" t="n">
         <v>8535.659203037463</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>57</v>
+        <v>57.83333333333334</v>
       </c>
       <c r="K51" t="n">
-        <v>5.82</v>
+        <v>3.8</v>
       </c>
       <c r="L51" t="n">
         <v>2.13</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>5.61</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45897.38541666666</v>
+        <v>45897.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>8211.5</v>
+        <v>8118</v>
       </c>
       <c r="I52" t="n">
         <v>8160.715079007619</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.98</v>
+        <v>-5.07</v>
       </c>
       <c r="L52" t="n">
-        <v>4.51</v>
+        <v>5.24</v>
       </c>
       <c r="M52" t="n">
         <v>0.73</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>5.48</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>8193.5</v>
+        <v>8936</v>
       </c>
       <c r="I53" t="n">
         <v>8428.178592268194</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.93</v>
+        <v>-10.08</v>
       </c>
       <c r="L53" t="n">
-        <v>2.35</v>
+        <v>10.82</v>
       </c>
       <c r="M53" t="n">
-        <v>0.82</v>
+        <v>5.75</v>
       </c>
       <c r="N53" t="n">
-        <v>2.11</v>
+        <v>10.34</v>
       </c>
       <c r="O53" t="n">
         <v>-1.93</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>7.95</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>8663</v>
+        <v>8434.5</v>
       </c>
       <c r="I54" t="n">
         <v>8503.826406996759</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.06</v>
+        <v>-5.61</v>
       </c>
       <c r="L54" t="n">
-        <v>4.05</v>
+        <v>6.12</v>
       </c>
       <c r="M54" t="n">
         <v>1.47</v>
       </c>
       <c r="N54" t="n">
-        <v>2.06</v>
+        <v>4.11</v>
       </c>
       <c r="O54" t="n">
         <v>10.34</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>6.17</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45931.55208333334</v>
+        <v>45933.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>8491.5</v>
+        <v>8679.5</v>
       </c>
       <c r="I55" t="n">
         <v>8550.241419896949</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.68</v>
+        <v>-2.9</v>
       </c>
       <c r="L55" t="n">
-        <v>2.69</v>
+        <v>3.27</v>
       </c>
       <c r="M55" t="n">
         <v>0.3</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.17</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>8676</v>
+        <v>8552.5</v>
       </c>
       <c r="I56" t="n">
         <v>8627.827680980628</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.04</v>
+        <v>-1.46</v>
       </c>
       <c r="L56" t="n">
         <v>3.21</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.14</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46036.55208333334</v>
+        <v>46038.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>7319.5</v>
+        <v>7707.5</v>
       </c>
       <c r="I57" t="n">
         <v>7630.399361374984</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>91.16666666666667</v>
+        <v>93</v>
       </c>
       <c r="K57" t="n">
-        <v>14.42</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L57" t="n">
         <v>3.13</v>
@@ -3690,7 +4373,7 @@
         <v>1.22</v>
       </c>
       <c r="N57" t="n">
-        <v>3.34</v>
+        <v>5.51</v>
       </c>
       <c r="O57" t="n">
         <v>-1.62</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>7.29</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46056.55208333334</v>
+        <v>46057.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>7591</v>
+        <v>7285.5</v>
       </c>
       <c r="I58" t="n">
         <v>7373.921142196066</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.51</v>
+        <v>-5.48</v>
       </c>
       <c r="L58" t="n">
-        <v>4.92</v>
+        <v>5.84</v>
       </c>
       <c r="M58" t="n">
-        <v>0.61</v>
+        <v>1.51</v>
       </c>
       <c r="N58" t="n">
-        <v>2.2</v>
+        <v>3.83</v>
       </c>
       <c r="O58" t="n">
         <v>5.51</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.94</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46079.38541666666</v>
+        <v>46079.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>6641.5</v>
+        <v>6678.5</v>
       </c>
       <c r="I59" t="n">
         <v>6644.452901079006</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>8.84</v>
+        <v>8.33</v>
       </c>
       <c r="L59" t="n">
         <v>2.61</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.1</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46094.38541666666</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>6383.5</v>
+        <v>6346</v>
       </c>
       <c r="I60" t="n">
         <v>6360.405450047672</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.42</v>
+        <v>-4.98</v>
       </c>
       <c r="L60" t="n">
-        <v>4.5</v>
+        <v>5.38</v>
       </c>
       <c r="M60" t="n">
         <v>2.06</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.6</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46106.55208333334</v>
+        <v>46108.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>6431</v>
+        <v>6721</v>
       </c>
       <c r="I61" t="n">
         <v>6535.830355855858</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>12</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.34</v>
+        <v>-5.91</v>
       </c>
       <c r="L61" t="n">
-        <v>2.77</v>
+        <v>8.19</v>
       </c>
       <c r="M61" t="n">
-        <v>2.64</v>
+        <v>2.79</v>
       </c>
       <c r="N61" t="n">
-        <v>4.78</v>
+        <v>5.14</v>
       </c>
       <c r="O61" t="n">
         <v>-2.54</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.43</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>9120.5</v>
+        <v>9018</v>
       </c>
       <c r="I62" t="n">
         <v>9070.51559731992</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>35.7</v>
+        <v>34.18</v>
       </c>
       <c r="L62" t="n">
         <v>3.36</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>5.39</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>9027.5</v>
+        <v>9301.5</v>
       </c>
       <c r="I63" t="n">
         <v>9274.89086735319</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.11</v>
+        <v>-3.14</v>
       </c>
       <c r="L63" t="n">
-        <v>2.02</v>
+        <v>3.97</v>
       </c>
       <c r="M63" t="n">
         <v>0.05</v>
       </c>
       <c r="N63" t="n">
-        <v>1.32</v>
+        <v>4.74</v>
       </c>
       <c r="O63" t="n">
         <v>-2.03</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.69</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46181.55208333334</v>
+        <v>46182.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>9704</v>
+        <v>9539</v>
       </c>
       <c r="I64" t="n">
         <v>9669.814898743</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K64" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="L64" t="n">
         <v>3.78</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>8.77</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46196.55208333334</v>
+        <v>46197.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>9864</v>
+        <v>10155</v>
       </c>
       <c r="I65" t="n">
         <v>9891.132781287302</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.41</v>
+        <v>-6.46</v>
       </c>
       <c r="L65" t="n">
-        <v>4.05</v>
+        <v>7.81</v>
       </c>
       <c r="M65" t="n">
         <v>1.44</v>
       </c>
       <c r="N65" t="n">
-        <v>2.53</v>
+        <v>6.28</v>
       </c>
       <c r="O65" t="n">
         <v>-0.44</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>7.2</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46225.38541666666</v>
+        <v>46225.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>11245</v>
+        <v>10777</v>
       </c>
       <c r="I66" t="n">
         <v>11072.92363977206</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>10.73</v>
+        <v>6.13</v>
       </c>
       <c r="L66" t="n">
         <v>2.76</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>9.59</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46238.55208333334</v>
+        <v>46239.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>11584</v>
+        <v>11731</v>
       </c>
       <c r="I67" t="n">
         <v>11724.95923845461</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>-7.49</v>
+        <v>-8.85</v>
       </c>
       <c r="L67" t="n">
-        <v>8.52</v>
+        <v>9.59</v>
       </c>
       <c r="M67" t="n">
         <v>4.84</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.06</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46273.55208333334</v>
+        <v>46274.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>11785</v>
+        <v>11645</v>
       </c>
       <c r="I68" t="n">
         <v>11660.54636919604</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K68" t="n">
-        <v>0.46</v>
+        <v>-0.73</v>
       </c>
       <c r="L68" t="n">
         <v>3.52</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>64</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7314,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.4</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7324,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7334,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7344,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7354,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7364,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="11">
@@ -6539,7 +7374,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +7384,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -6559,7 +7394,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>74.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6569,7 +7404,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.61</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7414,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.78</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.38</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7434,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>95.90000000000001</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7444,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43.3</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7454,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.77</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7464,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7474,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7484,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7494,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7504,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.29</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="25">
@@ -6679,7 +7514,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.84</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="26">
@@ -6689,7 +7524,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.99</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="27">
@@ -6699,7 +7534,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.56</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="28">
@@ -6709,7 +7544,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
